--- a/extra_data.xlsx
+++ b/extra_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10514"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/toyoho/Documents/study/704-Python/Webアプリ20230513/Streamlit/streamlit_test/pages/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/toyoho/Desktop/Python/Webアプリ20230513/Streamlit/streamlit_test/pages/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8399CC38-DD15-6240-BA97-6358360B9114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7478C2CD-DB66-DD4E-94E4-7BC63963604F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52820" yWindow="5580" windowWidth="28300" windowHeight="17440" xr2:uid="{13267BEF-5276-7649-830A-99174135B02F}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{13267BEF-5276-7649-830A-99174135B02F}"/>
   </bookViews>
   <sheets>
     <sheet name="coastline_simple" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -90,6 +90,14 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -118,8 +126,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -436,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EFC3F50-7D4B-F143-8236-0E63F03CA69A}">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -644,110 +655,110 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20">
-        <v>36.800961698367999</v>
-      </c>
-      <c r="B20">
-        <v>137.15581468346599</v>
-      </c>
-      <c r="C20">
+      <c r="A20" s="1">
+        <v>37.156614669406302</v>
+      </c>
+      <c r="B20" s="1">
+        <v>138.168328364014</v>
+      </c>
+      <c r="C20" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21">
-        <v>36.768544089585099</v>
-      </c>
-      <c r="B21">
-        <v>137.106807276578</v>
-      </c>
-      <c r="C21">
+      <c r="A21" s="1">
+        <v>36.927815953440003</v>
+      </c>
+      <c r="B21" s="1">
+        <v>137.432300669608</v>
+      </c>
+      <c r="C21" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22">
-        <v>35.606248209699402</v>
-      </c>
-      <c r="B22">
-        <v>135.92519421198699</v>
-      </c>
-      <c r="C22">
+      <c r="A22" s="1">
+        <v>36.7627943484949</v>
+      </c>
+      <c r="B22" s="1">
+        <v>137.34355863816899</v>
+      </c>
+      <c r="C22" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23">
-        <v>35.719926942836302</v>
-      </c>
-      <c r="B23">
-        <v>135.00001464338399</v>
-      </c>
-      <c r="C23">
+      <c r="A23" s="1">
+        <v>36.762761618824598</v>
+      </c>
+      <c r="B23" s="1">
+        <v>137.11292030638799</v>
+      </c>
+      <c r="C23" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24">
-        <v>35.389948809857898</v>
-      </c>
-      <c r="B24">
-        <v>132.676061970115</v>
-      </c>
-      <c r="C24">
+      <c r="A24" s="1">
+        <v>36.852978941172601</v>
+      </c>
+      <c r="B24" s="1">
+        <v>136.985015568118</v>
+      </c>
+      <c r="C24" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25">
-        <v>34.982349833394501</v>
-      </c>
-      <c r="B25">
-        <v>131.996748180851</v>
-      </c>
-      <c r="C25">
+      <c r="A25" s="1">
+        <v>37.163729307613899</v>
+      </c>
+      <c r="B25" s="1">
+        <v>137.033254057969</v>
+      </c>
+      <c r="C25" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26">
-        <v>34.140681369084596</v>
-      </c>
-      <c r="B26">
-        <v>130.852640830376</v>
-      </c>
-      <c r="C26">
+      <c r="A26" s="1">
+        <v>37.494428242899801</v>
+      </c>
+      <c r="B26" s="1">
+        <v>137.319771215896</v>
+      </c>
+      <c r="C26" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27">
-        <v>33.833788526396503</v>
-      </c>
-      <c r="B27">
-        <v>131.94986921448699</v>
-      </c>
-      <c r="C27">
+      <c r="A27" s="1">
+        <v>37.339883107734401</v>
+      </c>
+      <c r="B27" s="1">
+        <v>136.72106068066901</v>
+      </c>
+      <c r="C27" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28">
-        <v>34.498182795367597</v>
-      </c>
-      <c r="B28">
-        <v>133.21863696594701</v>
-      </c>
-      <c r="C28">
+      <c r="A28" s="1">
+        <v>36.887636707904598</v>
+      </c>
+      <c r="B28" s="1">
+        <v>136.748910214972</v>
+      </c>
+      <c r="C28" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>34.578834235631803</v>
+        <v>35.606248209699402</v>
       </c>
       <c r="B29">
-        <v>134.89440481001699</v>
+        <v>135.92519421198699</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -755,10 +766,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>33.3945188866088</v>
+        <v>35.719926942836302</v>
       </c>
       <c r="B30">
-        <v>135.70975823698001</v>
+        <v>135.00001464338399</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -766,10 +777,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>34.664621211708003</v>
+        <v>35.389948809857898</v>
       </c>
       <c r="B31">
-        <v>136.76089822118701</v>
+        <v>132.676061970115</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -777,225 +788,233 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
+        <v>34.982349833394501</v>
+      </c>
+      <c r="B32">
+        <v>131.996748180851</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>34.140681369084596</v>
+      </c>
+      <c r="B33">
+        <v>130.852640830376</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>33.833788526396503</v>
+      </c>
+      <c r="B34">
+        <v>131.94986921448699</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>34.498182795367597</v>
+      </c>
+      <c r="B35">
+        <v>133.21863696594701</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>34.578834235631803</v>
+      </c>
+      <c r="B36">
+        <v>134.89440481001699</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>33.3945188866088</v>
+      </c>
+      <c r="B37">
+        <v>135.70975823698001</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>34.664621211708003</v>
+      </c>
+      <c r="B38">
+        <v>136.76089822118701</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
         <v>34.617255201780999</v>
       </c>
-      <c r="B32">
+      <c r="B39">
         <v>138.08576390026499</v>
       </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33">
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
         <v>35.280204871102697</v>
       </c>
-      <c r="B33">
+      <c r="B40">
         <v>139.191325690273</v>
       </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34">
+      <c r="C40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
         <v>35.045073452807898</v>
       </c>
-      <c r="B34">
+      <c r="B41">
         <v>139.978340017997</v>
       </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35">
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
         <v>35.646244836984302</v>
       </c>
-      <c r="B35">
+      <c r="B42">
         <v>140.52760167315799</v>
       </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36">
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
         <v>37.671752091697002</v>
       </c>
-      <c r="B36">
+      <c r="B43">
         <v>141.09708071683201</v>
       </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37">
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
         <v>39.070537793496698</v>
       </c>
-      <c r="B37">
+      <c r="B44">
         <v>141.91681836433199</v>
       </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38">
+      <c r="C44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
         <v>41.2710686834209</v>
       </c>
-      <c r="B38">
+      <c r="B45">
         <v>141.39757867721599</v>
       </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39">
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
         <v>41.170289448862</v>
       </c>
-      <c r="B39">
+      <c r="B46">
         <v>140.412694766594</v>
       </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40">
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
         <v>41.153132698623303</v>
       </c>
-      <c r="B40">
+      <c r="B47">
         <v>140.38702517246901</v>
       </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42">
-        <v>34.369474665616004</v>
-      </c>
-      <c r="B42">
-        <v>133.96068353073801</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="D42" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43">
-        <v>33.9330271484558</v>
-      </c>
-      <c r="B43">
-        <v>132.875694602918</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44">
-        <v>33.390932631009299</v>
-      </c>
-      <c r="B44">
-        <v>132.375730040825</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45">
-        <v>32.796997242667402</v>
-      </c>
-      <c r="B45">
-        <v>132.77968553958601</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46">
-        <v>33.484029892956002</v>
-      </c>
-      <c r="B46">
-        <v>133.66080944389199</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47">
-        <v>33.234990069255602</v>
-      </c>
-      <c r="B47">
-        <v>134.111070356977</v>
-      </c>
       <c r="C47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48">
-        <v>33.841222816320901</v>
-      </c>
-      <c r="B48">
-        <v>134.69094928853701</v>
-      </c>
-      <c r="C48">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>34.326140760843998</v>
+        <v>34.369474665616004</v>
       </c>
       <c r="B49">
-        <v>133.907835214138</v>
+        <v>133.96068353073801</v>
       </c>
       <c r="C49">
         <v>0</v>
+      </c>
+      <c r="D49" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>34.369474665616004</v>
+        <v>33.9330271484558</v>
       </c>
       <c r="B50">
-        <v>133.96068353073801</v>
+        <v>132.875694602918</v>
       </c>
       <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51">
+        <v>33.390932631009299</v>
+      </c>
+      <c r="B51">
+        <v>132.375730040825</v>
+      </c>
+      <c r="C51">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>33.858700574232898</v>
+        <v>32.796997242667402</v>
       </c>
       <c r="B52">
-        <v>130.83190476357299</v>
+        <v>132.77968553958601</v>
       </c>
       <c r="C52">
         <v>0</v>
-      </c>
-      <c r="D52" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>33.309380080641802</v>
+        <v>33.484029892956002</v>
       </c>
       <c r="B53">
-        <v>129.54029923965001</v>
+        <v>133.66080944389199</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1003,10 +1022,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54">
-        <v>32.827092071491002</v>
+        <v>33.234990069255602</v>
       </c>
       <c r="B54">
-        <v>129.942291966216</v>
+        <v>134.111070356977</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1014,10 +1033,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55">
-        <v>31.2850822398334</v>
+        <v>33.841222816320901</v>
       </c>
       <c r="B55">
-        <v>130.319867429152</v>
+        <v>134.69094928853701</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1025,10 +1044,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56">
-        <v>31.2443085990786</v>
+        <v>34.326140760843998</v>
       </c>
       <c r="B56">
-        <v>130.95230343239999</v>
+        <v>133.907835214138</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1036,45 +1055,114 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57">
-        <v>31.609308458424302</v>
+        <v>34.369474665616004</v>
       </c>
       <c r="B57">
-        <v>131.49072704568201</v>
+        <v>133.96068353073801</v>
       </c>
       <c r="C57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58">
-        <v>32.9482388068744</v>
-      </c>
-      <c r="B58">
-        <v>131.931285639393</v>
-      </c>
-      <c r="C58">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59">
-        <v>33.874082715755897</v>
+        <v>33.858700574232898</v>
       </c>
       <c r="B59">
-        <v>130.86646583077999</v>
+        <v>130.83190476357299</v>
       </c>
       <c r="C59">
         <v>0</v>
+      </c>
+      <c r="D59" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60">
+        <v>33.309380080641802</v>
+      </c>
+      <c r="B60">
+        <v>129.54029923965001</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61">
+        <v>32.827092071491002</v>
+      </c>
+      <c r="B61">
+        <v>129.942291966216</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62">
+        <v>31.2850822398334</v>
+      </c>
+      <c r="B62">
+        <v>130.319867429152</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63">
+        <v>31.2443085990786</v>
+      </c>
+      <c r="B63">
+        <v>130.95230343239999</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64">
+        <v>31.609308458424302</v>
+      </c>
+      <c r="B64">
+        <v>131.49072704568201</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>32.9482388068744</v>
+      </c>
+      <c r="B65">
+        <v>131.931285639393</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>33.874082715755897</v>
+      </c>
+      <c r="B66">
+        <v>130.86646583077999</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
         <v>33.858700574232898</v>
       </c>
-      <c r="B60">
+      <c r="B67">
         <v>130.83190476357299</v>
       </c>
-      <c r="C60">
+      <c r="C67">
         <v>0</v>
       </c>
     </row>

--- a/extra_data.xlsx
+++ b/extra_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/toyoho/Documents/study/704-Python/Webアプリ_main134_20230513/Streamlit/streamlit_main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A65580-DD36-6740-AD1C-7D0B9B8BC709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AEE794-D5C2-774B-9836-728F91E6709E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58280" yWindow="800" windowWidth="38400" windowHeight="21100" xr2:uid="{13267BEF-5276-7649-830A-99174135B02F}"/>
+    <workbookView xWindow="54780" yWindow="1640" windowWidth="38400" windowHeight="21100" xr2:uid="{13267BEF-5276-7649-830A-99174135B02F}"/>
   </bookViews>
   <sheets>
     <sheet name="coastline_detail" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
   <si>
     <t>Latitude</t>
     <phoneticPr fontId="1"/>
@@ -224,6 +224,52 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>ウルップ島</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥尻島</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">オクシリトウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利尻島</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">リシリトウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>礼文島</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">レブントウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>色丹島</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">シコタントウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>国後島</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">クナシリトウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>択捉島</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">エトロフトウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -2069,6 +2115,432 @@
                 <c:pt idx="572">
                   <c:v>129.27337646484401</c:v>
                 </c:pt>
+                <c:pt idx="574">
+                  <c:v>150.59509277343801</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>150.194091796875</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>150.04577636718801</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>149.91394042968801</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>149.67224121093801</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>149.44152832031301</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>149.69421386718801</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>150.32043457031301</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>150.60607910156301</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>139.56069946289099</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>139.55108642578099</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>139.52087402343801</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>139.50302124023401</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>139.44808959960901</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>139.41787719726599</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>139.41101074218801</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>139.42886352539099</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>139.48104858398401</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>139.56207275390599</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>141.19663238525399</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>141.22718811035199</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>141.22787475585901</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>141.25465393066401</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>141.26358032226599</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>141.27044677734401</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>141.28074645996099</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>141.281776428223</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>141.30409240722699</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>141.32537841796901</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>141.330528259277</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>141.28555297851599</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>141.23851776123101</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>141.20075225830101</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>141.15886688232399</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>141.13655090332</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>141.12522125244101</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>141.137580871582</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>141.13243103027301</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>141.157150268555</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>141.19594573974601</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>141.03630065918</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>141.06994628906301</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>141.05758666992199</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>141.05278015136699</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>141.05827331543</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>141.04454040527301</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>141.025314331055</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>141.02188110351599</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>140.99922180175801</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>140.98068237304699</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>140.99235534668</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>140.96488952636699</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>140.97106933593801</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>141.01089477539099</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>141.03492736816401</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>141.03561401367199</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>146.65924072265599</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>146.57684326171901</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>146.71691894531301</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>146.84875488281301</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>146.92291259765599</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>146.79931640625</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>146.70318603515599</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>146.65924072265599</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>146.173095703125</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>146.34613037109401</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>146.57684326171901</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>146.55487060546901</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>146.49993896484401</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>146.41204833984401</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>146.31042480468801</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>146.10168457031301</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>146.04675292968801</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>145.90118408203099</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>145.89294433593801</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>145.83251953125</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>145.78308105468801</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>145.59631347656301</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>145.56884765625</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>145.43701171875</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>145.39581298828099</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>145.73638916015599</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>145.73913574218801</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>145.97259521484401</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>146.02203369140599</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>146.16485595703099</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>148.90319824218801</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>148.82354736328099</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>148.88671875</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>148.853759765625</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>148.62579345703099</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>148.40606689453099</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>148.31268310546901</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>147.92541503906301</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>147.77984619140599</c:v>
+                </c:pt>
+                <c:pt idx="675">
+                  <c:v>147.68646240234401</c:v>
+                </c:pt>
+                <c:pt idx="676">
+                  <c:v>147.60681152343801</c:v>
+                </c:pt>
+                <c:pt idx="677">
+                  <c:v>147.65350341796901</c:v>
+                </c:pt>
+                <c:pt idx="678">
+                  <c:v>147.50518798828099</c:v>
+                </c:pt>
+                <c:pt idx="679">
+                  <c:v>147.34039306640599</c:v>
+                </c:pt>
+                <c:pt idx="680">
+                  <c:v>147.20855712890599</c:v>
+                </c:pt>
+                <c:pt idx="681">
+                  <c:v>146.97784423828099</c:v>
+                </c:pt>
+                <c:pt idx="682">
+                  <c:v>146.87072753906301</c:v>
+                </c:pt>
+                <c:pt idx="683">
+                  <c:v>146.93389892578099</c:v>
+                </c:pt>
+                <c:pt idx="684">
+                  <c:v>147.02728271484401</c:v>
+                </c:pt>
+                <c:pt idx="685">
+                  <c:v>147.02728271484401</c:v>
+                </c:pt>
+                <c:pt idx="686">
+                  <c:v>147.117919921875</c:v>
+                </c:pt>
+                <c:pt idx="687">
+                  <c:v>147.20306396484401</c:v>
+                </c:pt>
+                <c:pt idx="688">
+                  <c:v>147.09045410156301</c:v>
+                </c:pt>
+                <c:pt idx="689">
+                  <c:v>147.11585998535199</c:v>
+                </c:pt>
+                <c:pt idx="690">
+                  <c:v>147.19276428222699</c:v>
+                </c:pt>
+                <c:pt idx="691">
+                  <c:v>147.24151611328099</c:v>
+                </c:pt>
+                <c:pt idx="692">
+                  <c:v>147.26417541503901</c:v>
+                </c:pt>
+                <c:pt idx="693">
+                  <c:v>147.38433837890599</c:v>
+                </c:pt>
+                <c:pt idx="694">
+                  <c:v>147.48664855957</c:v>
+                </c:pt>
+                <c:pt idx="695">
+                  <c:v>147.51274108886699</c:v>
+                </c:pt>
+                <c:pt idx="696">
+                  <c:v>147.52853393554699</c:v>
+                </c:pt>
+                <c:pt idx="697">
+                  <c:v>147.49557495117199</c:v>
+                </c:pt>
+                <c:pt idx="698">
+                  <c:v>147.50999450683599</c:v>
+                </c:pt>
+                <c:pt idx="699">
+                  <c:v>147.57247924804699</c:v>
+                </c:pt>
+                <c:pt idx="700">
+                  <c:v>147.63015747070301</c:v>
+                </c:pt>
+                <c:pt idx="701">
+                  <c:v>147.69813537597699</c:v>
+                </c:pt>
+                <c:pt idx="702">
+                  <c:v>147.69332885742199</c:v>
+                </c:pt>
+                <c:pt idx="703">
+                  <c:v>147.73727416992199</c:v>
+                </c:pt>
+                <c:pt idx="704">
+                  <c:v>147.82653808593801</c:v>
+                </c:pt>
+                <c:pt idx="705">
+                  <c:v>147.84645080566401</c:v>
+                </c:pt>
+                <c:pt idx="706">
+                  <c:v>147.88352966308599</c:v>
+                </c:pt>
+                <c:pt idx="707">
+                  <c:v>147.86293029785199</c:v>
+                </c:pt>
+                <c:pt idx="708">
+                  <c:v>147.85263061523401</c:v>
+                </c:pt>
+                <c:pt idx="709">
+                  <c:v>147.91854858398401</c:v>
+                </c:pt>
+                <c:pt idx="710">
+                  <c:v>147.96318054199199</c:v>
+                </c:pt>
+                <c:pt idx="711">
+                  <c:v>148.03390502929699</c:v>
+                </c:pt>
+                <c:pt idx="712">
+                  <c:v>148.14308166503901</c:v>
+                </c:pt>
+                <c:pt idx="713">
+                  <c:v>148.34701538085901</c:v>
+                </c:pt>
+                <c:pt idx="714">
+                  <c:v>148.47953796386699</c:v>
+                </c:pt>
+                <c:pt idx="715">
+                  <c:v>148.48159790039099</c:v>
+                </c:pt>
+                <c:pt idx="716">
+                  <c:v>148.57772827148401</c:v>
+                </c:pt>
+                <c:pt idx="717">
+                  <c:v>148.63815307617199</c:v>
+                </c:pt>
+                <c:pt idx="718">
+                  <c:v>148.65051269531301</c:v>
+                </c:pt>
+                <c:pt idx="719">
+                  <c:v>148.78578186035199</c:v>
+                </c:pt>
+                <c:pt idx="720">
+                  <c:v>148.87023925781301</c:v>
+                </c:pt>
+                <c:pt idx="721">
+                  <c:v>148.90319824218801</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -3760,6 +4232,432 @@
                 </c:pt>
                 <c:pt idx="572">
                   <c:v>34.502029794434598</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>46.2558468184803</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>45.947330315089303</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>45.817315080406303</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>45.821143400794703</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>45.602509015103003</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>45.575600209477997</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>45.859412127907603</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>46.217851767402998</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>46.263442671779899</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>42.262065510743902</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>42.224449701009803</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>42.185793905378503</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>42.089050952191698</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>42.064587244630701</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>42.118598682815701</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>42.173581898327797</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>42.230551085522897</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>42.231567925608601</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>42.262065510743902</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>45.262321932396297</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>45.248787816986301</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>45.237426337600901</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>45.237668094862101</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>45.233074531011603</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>45.236701059645704</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>45.2350087084167</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>45.227271603821301</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>45.214696562430099</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>45.184456718804697</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>45.150084757405601</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>45.110119454608601</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>45.097760877277103</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>45.115207502941701</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>45.148389828528401</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>45.176470718550398</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>45.187360441176899</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>45.189296173804401</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>45.214938416377997</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>45.240085610902597</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>45.262563583714297</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>45.463501855252503</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>45.426407377512803</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>45.400378517255398</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>45.344424104522403</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>45.316908979003898</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>45.274403238298397</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>45.274886437048899</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>45.310148833244902</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>45.324633872462201</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>45.382537001817298</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>45.4230339427545</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>45.4384537131942</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>45.462538670870302</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>45.430744354565299</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>45.440862671781801</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>45.463020265118303</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>43.711564246658497</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>43.8127292976109</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>43.836507977091003</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>43.897892391257997</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>43.826601345053803</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>43.769110452366199</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>43.733398628766103</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>43.711564246658497</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>44.514134729871103</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>44.420049661901501</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>44.443585145921197</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>44.376876658782898</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>44.349386343895297</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>44.372950260724402</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>44.272738162790901</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>44.260937250399202</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>44.184173573254</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>44.101393064498502</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>44.0204715633541</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>44.0204715633541</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>43.939439464527503</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>43.876118060753598</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>43.7294293330051</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>43.719504942691103</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>43.8285828030142</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>44.050089820756803</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>44.081666311450498</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>44.302230078625499</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>44.396504700115599</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>44.520010011339899</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>45.490945692627299</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>45.448570648115798</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>45.4061637451601</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>45.340563138898602</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>45.327047685672603</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>45.230414929592897</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>45.213003555994</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>44.9745137056399</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>44.949249266611503</c:v>
+                </c:pt>
+                <c:pt idx="675">
+                  <c:v>45.003651156871904</c:v>
+                </c:pt>
+                <c:pt idx="676">
+                  <c:v>44.935640729718401</c:v>
+                </c:pt>
+                <c:pt idx="677">
+                  <c:v>44.904523389609302</c:v>
+                </c:pt>
+                <c:pt idx="678">
+                  <c:v>44.7798855027728</c:v>
+                </c:pt>
+                <c:pt idx="679">
+                  <c:v>44.707706221835402</c:v>
+                </c:pt>
+                <c:pt idx="680">
+                  <c:v>44.563077307578901</c:v>
+                </c:pt>
+                <c:pt idx="681">
+                  <c:v>44.429857265397203</c:v>
+                </c:pt>
+                <c:pt idx="682">
+                  <c:v>44.4416242175881</c:v>
+                </c:pt>
+                <c:pt idx="683">
+                  <c:v>44.545462718849798</c:v>
+                </c:pt>
+                <c:pt idx="684">
+                  <c:v>44.592423107178703</c:v>
+                </c:pt>
+                <c:pt idx="685">
+                  <c:v>44.654977979262902</c:v>
+                </c:pt>
+                <c:pt idx="686">
+                  <c:v>44.6354368225686</c:v>
+                </c:pt>
+                <c:pt idx="687">
+                  <c:v>44.748683899968299</c:v>
+                </c:pt>
+                <c:pt idx="688">
+                  <c:v>44.789632547614097</c:v>
+                </c:pt>
+                <c:pt idx="689">
+                  <c:v>44.827143305192799</c:v>
+                </c:pt>
+                <c:pt idx="690">
+                  <c:v>44.797428998555702</c:v>
+                </c:pt>
+                <c:pt idx="691">
+                  <c:v>44.8086345514958</c:v>
+                </c:pt>
+                <c:pt idx="692">
+                  <c:v>44.868036310187499</c:v>
+                </c:pt>
+                <c:pt idx="693">
+                  <c:v>44.9142493687471</c:v>
+                </c:pt>
+                <c:pt idx="694">
+                  <c:v>44.989084282761397</c:v>
+                </c:pt>
+                <c:pt idx="695">
+                  <c:v>44.9910267465945</c:v>
+                </c:pt>
+                <c:pt idx="696">
+                  <c:v>45.090974638356599</c:v>
+                </c:pt>
+                <c:pt idx="697">
+                  <c:v>45.109877155278099</c:v>
+                </c:pt>
+                <c:pt idx="698">
+                  <c:v>45.1161766035749</c:v>
+                </c:pt>
+                <c:pt idx="699">
+                  <c:v>45.103092356408602</c:v>
+                </c:pt>
+                <c:pt idx="700">
+                  <c:v>45.075460206883598</c:v>
+                </c:pt>
+                <c:pt idx="701">
+                  <c:v>45.102123033596399</c:v>
+                </c:pt>
+                <c:pt idx="702">
+                  <c:v>45.144757668358203</c:v>
+                </c:pt>
+                <c:pt idx="703">
+                  <c:v>45.192199649314503</c:v>
+                </c:pt>
+                <c:pt idx="704">
+                  <c:v>45.216389518465498</c:v>
+                </c:pt>
+                <c:pt idx="705">
+                  <c:v>45.2067148051106</c:v>
+                </c:pt>
+                <c:pt idx="706">
+                  <c:v>45.2555552778921</c:v>
+                </c:pt>
+                <c:pt idx="707">
+                  <c:v>45.262321932396297</c:v>
+                </c:pt>
+                <c:pt idx="708">
+                  <c:v>45.364689854189798</c:v>
+                </c:pt>
+                <c:pt idx="709">
+                  <c:v>45.435562827127796</c:v>
+                </c:pt>
+                <c:pt idx="710">
+                  <c:v>45.419178341904598</c:v>
+                </c:pt>
+                <c:pt idx="711">
+                  <c:v>45.266671498748998</c:v>
+                </c:pt>
+                <c:pt idx="712">
+                  <c:v>45.254588547134198</c:v>
+                </c:pt>
+                <c:pt idx="713">
+                  <c:v>45.292761898494</c:v>
+                </c:pt>
+                <c:pt idx="714">
+                  <c:v>45.390735154248901</c:v>
+                </c:pt>
+                <c:pt idx="715">
+                  <c:v>45.416286468478503</c:v>
+                </c:pt>
+                <c:pt idx="716">
+                  <c:v>45.485650554296299</c:v>
+                </c:pt>
+                <c:pt idx="717">
+                  <c:v>45.504421980400799</c:v>
+                </c:pt>
+                <c:pt idx="718">
+                  <c:v>45.536655719680297</c:v>
+                </c:pt>
+                <c:pt idx="719">
+                  <c:v>45.5525252513401</c:v>
+                </c:pt>
+                <c:pt idx="720">
+                  <c:v>45.532326888097302</c:v>
+                </c:pt>
+                <c:pt idx="721">
+                  <c:v>45.489501613357902</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10731,7 +11629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{413D18A8-6BFE-9C43-9CB2-607B9D9EBE41}">
-  <dimension ref="B1:K574"/>
+  <dimension ref="B1:K723"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="2:11">
@@ -16958,6 +17856,1589 @@
         <v>34.502029794434598</v>
       </c>
       <c r="D574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="2:5">
+      <c r="B576" s="3">
+        <v>150.59509277343801</v>
+      </c>
+      <c r="C576" s="4">
+        <v>46.2558468184803</v>
+      </c>
+      <c r="D576">
+        <v>0</v>
+      </c>
+      <c r="E576" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="577" spans="2:5">
+      <c r="B577" s="3">
+        <v>150.194091796875</v>
+      </c>
+      <c r="C577" s="4">
+        <v>45.947330315089303</v>
+      </c>
+      <c r="D577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="2:5">
+      <c r="B578" s="3">
+        <v>150.04577636718801</v>
+      </c>
+      <c r="C578" s="4">
+        <v>45.817315080406303</v>
+      </c>
+      <c r="D578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="2:5">
+      <c r="B579" s="3">
+        <v>149.91394042968801</v>
+      </c>
+      <c r="C579" s="4">
+        <v>45.821143400794703</v>
+      </c>
+      <c r="D579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="2:5">
+      <c r="B580" s="3">
+        <v>149.67224121093801</v>
+      </c>
+      <c r="C580" s="4">
+        <v>45.602509015103003</v>
+      </c>
+      <c r="D580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="2:5">
+      <c r="B581" s="3">
+        <v>149.44152832031301</v>
+      </c>
+      <c r="C581" s="4">
+        <v>45.575600209477997</v>
+      </c>
+      <c r="D581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="2:5">
+      <c r="B582" s="3">
+        <v>149.69421386718801</v>
+      </c>
+      <c r="C582" s="4">
+        <v>45.859412127907603</v>
+      </c>
+      <c r="D582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="2:5">
+      <c r="B583" s="3">
+        <v>150.32043457031301</v>
+      </c>
+      <c r="C583" s="4">
+        <v>46.217851767402998</v>
+      </c>
+      <c r="D583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="2:5">
+      <c r="B584" s="3">
+        <v>150.60607910156301</v>
+      </c>
+      <c r="C584" s="4">
+        <v>46.263442671779899</v>
+      </c>
+      <c r="D584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="2:5">
+      <c r="B586" s="3">
+        <v>139.56069946289099</v>
+      </c>
+      <c r="C586" s="4">
+        <v>42.262065510743902</v>
+      </c>
+      <c r="D586">
+        <v>0</v>
+      </c>
+      <c r="E586" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="587" spans="2:5">
+      <c r="B587" s="3">
+        <v>139.55108642578099</v>
+      </c>
+      <c r="C587" s="4">
+        <v>42.224449701009803</v>
+      </c>
+      <c r="D587">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="2:5">
+      <c r="B588" s="3">
+        <v>139.52087402343801</v>
+      </c>
+      <c r="C588" s="4">
+        <v>42.185793905378503</v>
+      </c>
+      <c r="D588">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589" spans="2:5">
+      <c r="B589" s="3">
+        <v>139.50302124023401</v>
+      </c>
+      <c r="C589" s="4">
+        <v>42.089050952191698</v>
+      </c>
+      <c r="D589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="2:5">
+      <c r="B590" s="3">
+        <v>139.44808959960901</v>
+      </c>
+      <c r="C590" s="4">
+        <v>42.064587244630701</v>
+      </c>
+      <c r="D590">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591" spans="2:5">
+      <c r="B591" s="3">
+        <v>139.41787719726599</v>
+      </c>
+      <c r="C591" s="4">
+        <v>42.118598682815701</v>
+      </c>
+      <c r="D591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592" spans="2:5">
+      <c r="B592" s="3">
+        <v>139.41101074218801</v>
+      </c>
+      <c r="C592" s="4">
+        <v>42.173581898327797</v>
+      </c>
+      <c r="D592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593" spans="2:5">
+      <c r="B593" s="3">
+        <v>139.42886352539099</v>
+      </c>
+      <c r="C593" s="4">
+        <v>42.230551085522897</v>
+      </c>
+      <c r="D593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="2:5">
+      <c r="B594" s="3">
+        <v>139.48104858398401</v>
+      </c>
+      <c r="C594" s="4">
+        <v>42.231567925608601</v>
+      </c>
+      <c r="D594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="2:5">
+      <c r="B595" s="3">
+        <v>139.56207275390599</v>
+      </c>
+      <c r="C595" s="4">
+        <v>42.262065510743902</v>
+      </c>
+      <c r="D595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597" spans="2:5">
+      <c r="B597" s="3">
+        <v>141.19663238525399</v>
+      </c>
+      <c r="C597" s="4">
+        <v>45.262321932396297</v>
+      </c>
+      <c r="D597">
+        <v>0</v>
+      </c>
+      <c r="E597" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="598" spans="2:5">
+      <c r="B598" s="3">
+        <v>141.22718811035199</v>
+      </c>
+      <c r="C598" s="4">
+        <v>45.248787816986301</v>
+      </c>
+      <c r="D598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599" spans="2:5">
+      <c r="B599" s="3">
+        <v>141.22787475585901</v>
+      </c>
+      <c r="C599" s="4">
+        <v>45.237426337600901</v>
+      </c>
+      <c r="D599">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="600" spans="2:5">
+      <c r="B600" s="3">
+        <v>141.25465393066401</v>
+      </c>
+      <c r="C600" s="4">
+        <v>45.237668094862101</v>
+      </c>
+      <c r="D600">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601" spans="2:5">
+      <c r="B601" s="3">
+        <v>141.26358032226599</v>
+      </c>
+      <c r="C601" s="4">
+        <v>45.233074531011603</v>
+      </c>
+      <c r="D601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602" spans="2:5">
+      <c r="B602" s="3">
+        <v>141.27044677734401</v>
+      </c>
+      <c r="C602" s="4">
+        <v>45.236701059645704</v>
+      </c>
+      <c r="D602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603" spans="2:5">
+      <c r="B603" s="3">
+        <v>141.28074645996099</v>
+      </c>
+      <c r="C603" s="4">
+        <v>45.2350087084167</v>
+      </c>
+      <c r="D603">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604" spans="2:5">
+      <c r="B604" s="3">
+        <v>141.281776428223</v>
+      </c>
+      <c r="C604" s="4">
+        <v>45.227271603821301</v>
+      </c>
+      <c r="D604">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605" spans="2:5">
+      <c r="B605" s="3">
+        <v>141.30409240722699</v>
+      </c>
+      <c r="C605" s="4">
+        <v>45.214696562430099</v>
+      </c>
+      <c r="D605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="2:5">
+      <c r="B606" s="3">
+        <v>141.32537841796901</v>
+      </c>
+      <c r="C606" s="4">
+        <v>45.184456718804697</v>
+      </c>
+      <c r="D606">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607" spans="2:5">
+      <c r="B607" s="3">
+        <v>141.330528259277</v>
+      </c>
+      <c r="C607" s="4">
+        <v>45.150084757405601</v>
+      </c>
+      <c r="D607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="2:5">
+      <c r="B608" s="3">
+        <v>141.28555297851599</v>
+      </c>
+      <c r="C608" s="4">
+        <v>45.110119454608601</v>
+      </c>
+      <c r="D608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609" spans="2:5">
+      <c r="B609" s="3">
+        <v>141.23851776123101</v>
+      </c>
+      <c r="C609" s="4">
+        <v>45.097760877277103</v>
+      </c>
+      <c r="D609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610" spans="2:5">
+      <c r="B610" s="3">
+        <v>141.20075225830101</v>
+      </c>
+      <c r="C610" s="4">
+        <v>45.115207502941701</v>
+      </c>
+      <c r="D610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611" spans="2:5">
+      <c r="B611" s="3">
+        <v>141.15886688232399</v>
+      </c>
+      <c r="C611" s="4">
+        <v>45.148389828528401</v>
+      </c>
+      <c r="D611">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612" spans="2:5">
+      <c r="B612" s="3">
+        <v>141.13655090332</v>
+      </c>
+      <c r="C612" s="4">
+        <v>45.176470718550398</v>
+      </c>
+      <c r="D612">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613" spans="2:5">
+      <c r="B613" s="3">
+        <v>141.12522125244101</v>
+      </c>
+      <c r="C613" s="4">
+        <v>45.187360441176899</v>
+      </c>
+      <c r="D613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="2:5">
+      <c r="B614" s="3">
+        <v>141.137580871582</v>
+      </c>
+      <c r="C614" s="4">
+        <v>45.189296173804401</v>
+      </c>
+      <c r="D614">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615" spans="2:5">
+      <c r="B615" s="3">
+        <v>141.13243103027301</v>
+      </c>
+      <c r="C615" s="4">
+        <v>45.214938416377997</v>
+      </c>
+      <c r="D615">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616" spans="2:5">
+      <c r="B616" s="3">
+        <v>141.157150268555</v>
+      </c>
+      <c r="C616" s="4">
+        <v>45.240085610902597</v>
+      </c>
+      <c r="D616">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="2:5">
+      <c r="B617" s="3">
+        <v>141.19594573974601</v>
+      </c>
+      <c r="C617" s="4">
+        <v>45.262563583714297</v>
+      </c>
+      <c r="D617">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619" spans="2:5">
+      <c r="B619" s="3">
+        <v>141.03630065918</v>
+      </c>
+      <c r="C619" s="4">
+        <v>45.463501855252503</v>
+      </c>
+      <c r="D619">
+        <v>0</v>
+      </c>
+      <c r="E619" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="620" spans="2:5">
+      <c r="B620" s="3">
+        <v>141.06994628906301</v>
+      </c>
+      <c r="C620" s="4">
+        <v>45.426407377512803</v>
+      </c>
+      <c r="D620">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621" spans="2:5">
+      <c r="B621" s="3">
+        <v>141.05758666992199</v>
+      </c>
+      <c r="C621" s="4">
+        <v>45.400378517255398</v>
+      </c>
+      <c r="D621">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622" spans="2:5">
+      <c r="B622" s="3">
+        <v>141.05278015136699</v>
+      </c>
+      <c r="C622" s="4">
+        <v>45.344424104522403</v>
+      </c>
+      <c r="D622">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623" spans="2:5">
+      <c r="B623" s="3">
+        <v>141.05827331543</v>
+      </c>
+      <c r="C623" s="4">
+        <v>45.316908979003898</v>
+      </c>
+      <c r="D623">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624" spans="2:5">
+      <c r="B624" s="3">
+        <v>141.04454040527301</v>
+      </c>
+      <c r="C624" s="4">
+        <v>45.274403238298397</v>
+      </c>
+      <c r="D624">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625" spans="2:5">
+      <c r="B625" s="3">
+        <v>141.025314331055</v>
+      </c>
+      <c r="C625" s="4">
+        <v>45.274886437048899</v>
+      </c>
+      <c r="D625">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626" spans="2:5">
+      <c r="B626" s="3">
+        <v>141.02188110351599</v>
+      </c>
+      <c r="C626" s="4">
+        <v>45.310148833244902</v>
+      </c>
+      <c r="D626">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627" spans="2:5">
+      <c r="B627" s="3">
+        <v>140.99922180175801</v>
+      </c>
+      <c r="C627" s="4">
+        <v>45.324633872462201</v>
+      </c>
+      <c r="D627">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628" spans="2:5">
+      <c r="B628" s="3">
+        <v>140.98068237304699</v>
+      </c>
+      <c r="C628" s="4">
+        <v>45.382537001817298</v>
+      </c>
+      <c r="D628">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629" spans="2:5">
+      <c r="B629" s="3">
+        <v>140.99235534668</v>
+      </c>
+      <c r="C629" s="4">
+        <v>45.4230339427545</v>
+      </c>
+      <c r="D629">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630" spans="2:5">
+      <c r="B630" s="3">
+        <v>140.96488952636699</v>
+      </c>
+      <c r="C630" s="4">
+        <v>45.4384537131942</v>
+      </c>
+      <c r="D630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631" spans="2:5">
+      <c r="B631" s="3">
+        <v>140.97106933593801</v>
+      </c>
+      <c r="C631" s="4">
+        <v>45.462538670870302</v>
+      </c>
+      <c r="D631">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632" spans="2:5">
+      <c r="B632" s="3">
+        <v>141.01089477539099</v>
+      </c>
+      <c r="C632" s="4">
+        <v>45.430744354565299</v>
+      </c>
+      <c r="D632">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633" spans="2:5">
+      <c r="B633" s="3">
+        <v>141.03492736816401</v>
+      </c>
+      <c r="C633" s="4">
+        <v>45.440862671781801</v>
+      </c>
+      <c r="D633">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634" spans="2:5">
+      <c r="B634" s="3">
+        <v>141.03561401367199</v>
+      </c>
+      <c r="C634" s="4">
+        <v>45.463020265118303</v>
+      </c>
+      <c r="D634">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636" spans="2:5">
+      <c r="B636" s="3">
+        <v>146.65924072265599</v>
+      </c>
+      <c r="C636" s="4">
+        <v>43.711564246658497</v>
+      </c>
+      <c r="D636">
+        <v>0</v>
+      </c>
+      <c r="E636" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="637" spans="2:5">
+      <c r="B637" s="3">
+        <v>146.57684326171901</v>
+      </c>
+      <c r="C637" s="4">
+        <v>43.8127292976109</v>
+      </c>
+      <c r="D637">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638" spans="2:5">
+      <c r="B638" s="3">
+        <v>146.71691894531301</v>
+      </c>
+      <c r="C638" s="4">
+        <v>43.836507977091003</v>
+      </c>
+      <c r="D638">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639" spans="2:5">
+      <c r="B639" s="3">
+        <v>146.84875488281301</v>
+      </c>
+      <c r="C639" s="4">
+        <v>43.897892391257997</v>
+      </c>
+      <c r="D639">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640" spans="2:5">
+      <c r="B640" s="3">
+        <v>146.92291259765599</v>
+      </c>
+      <c r="C640" s="4">
+        <v>43.826601345053803</v>
+      </c>
+      <c r="D640">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641" spans="2:5">
+      <c r="B641" s="3">
+        <v>146.79931640625</v>
+      </c>
+      <c r="C641" s="4">
+        <v>43.769110452366199</v>
+      </c>
+      <c r="D641">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642" spans="2:5">
+      <c r="B642" s="3">
+        <v>146.70318603515599</v>
+      </c>
+      <c r="C642" s="4">
+        <v>43.733398628766103</v>
+      </c>
+      <c r="D642">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" spans="2:5">
+      <c r="B643" s="3">
+        <v>146.65924072265599</v>
+      </c>
+      <c r="C643" s="4">
+        <v>43.711564246658497</v>
+      </c>
+      <c r="D643">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645" spans="2:5">
+      <c r="B645" s="3">
+        <v>146.173095703125</v>
+      </c>
+      <c r="C645" s="4">
+        <v>44.514134729871103</v>
+      </c>
+      <c r="D645">
+        <v>0</v>
+      </c>
+      <c r="E645" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="646" spans="2:5">
+      <c r="B646" s="3">
+        <v>146.34613037109401</v>
+      </c>
+      <c r="C646" s="4">
+        <v>44.420049661901501</v>
+      </c>
+      <c r="D646">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647" spans="2:5">
+      <c r="B647" s="3">
+        <v>146.57684326171901</v>
+      </c>
+      <c r="C647" s="4">
+        <v>44.443585145921197</v>
+      </c>
+      <c r="D647">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648" spans="2:5">
+      <c r="B648" s="3">
+        <v>146.55487060546901</v>
+      </c>
+      <c r="C648" s="4">
+        <v>44.376876658782898</v>
+      </c>
+      <c r="D648">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="2:5">
+      <c r="B649" s="3">
+        <v>146.49993896484401</v>
+      </c>
+      <c r="C649" s="4">
+        <v>44.349386343895297</v>
+      </c>
+      <c r="D649">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650" spans="2:5">
+      <c r="B650" s="3">
+        <v>146.41204833984401</v>
+      </c>
+      <c r="C650" s="4">
+        <v>44.372950260724402</v>
+      </c>
+      <c r="D650">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651" spans="2:5">
+      <c r="B651" s="3">
+        <v>146.31042480468801</v>
+      </c>
+      <c r="C651" s="4">
+        <v>44.272738162790901</v>
+      </c>
+      <c r="D651">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652" spans="2:5">
+      <c r="B652" s="3">
+        <v>146.10168457031301</v>
+      </c>
+      <c r="C652" s="4">
+        <v>44.260937250399202</v>
+      </c>
+      <c r="D652">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="653" spans="2:5">
+      <c r="B653" s="3">
+        <v>146.04675292968801</v>
+      </c>
+      <c r="C653" s="4">
+        <v>44.184173573254</v>
+      </c>
+      <c r="D653">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="654" spans="2:5">
+      <c r="B654" s="3">
+        <v>145.90118408203099</v>
+      </c>
+      <c r="C654" s="4">
+        <v>44.101393064498502</v>
+      </c>
+      <c r="D654">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="655" spans="2:5">
+      <c r="B655" s="3">
+        <v>145.89294433593801</v>
+      </c>
+      <c r="C655" s="4">
+        <v>44.0204715633541</v>
+      </c>
+      <c r="D655">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="656" spans="2:5">
+      <c r="B656" s="3">
+        <v>145.83251953125</v>
+      </c>
+      <c r="C656" s="4">
+        <v>44.0204715633541</v>
+      </c>
+      <c r="D656">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657" spans="2:5">
+      <c r="B657" s="3">
+        <v>145.78308105468801</v>
+      </c>
+      <c r="C657" s="4">
+        <v>43.939439464527503</v>
+      </c>
+      <c r="D657">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658" spans="2:5">
+      <c r="B658" s="3">
+        <v>145.59631347656301</v>
+      </c>
+      <c r="C658" s="4">
+        <v>43.876118060753598</v>
+      </c>
+      <c r="D658">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="659" spans="2:5">
+      <c r="B659" s="3">
+        <v>145.56884765625</v>
+      </c>
+      <c r="C659" s="4">
+        <v>43.7294293330051</v>
+      </c>
+      <c r="D659">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="660" spans="2:5">
+      <c r="B660" s="3">
+        <v>145.43701171875</v>
+      </c>
+      <c r="C660" s="4">
+        <v>43.719504942691103</v>
+      </c>
+      <c r="D660">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="2:5">
+      <c r="B661" s="3">
+        <v>145.39581298828099</v>
+      </c>
+      <c r="C661" s="4">
+        <v>43.8285828030142</v>
+      </c>
+      <c r="D661">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="662" spans="2:5">
+      <c r="B662" s="3">
+        <v>145.73638916015599</v>
+      </c>
+      <c r="C662" s="4">
+        <v>44.050089820756803</v>
+      </c>
+      <c r="D662">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="663" spans="2:5">
+      <c r="B663" s="3">
+        <v>145.73913574218801</v>
+      </c>
+      <c r="C663" s="4">
+        <v>44.081666311450498</v>
+      </c>
+      <c r="D663">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="664" spans="2:5">
+      <c r="B664" s="3">
+        <v>145.97259521484401</v>
+      </c>
+      <c r="C664" s="4">
+        <v>44.302230078625499</v>
+      </c>
+      <c r="D664">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="665" spans="2:5">
+      <c r="B665" s="3">
+        <v>146.02203369140599</v>
+      </c>
+      <c r="C665" s="4">
+        <v>44.396504700115599</v>
+      </c>
+      <c r="D665">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666" spans="2:5">
+      <c r="B666" s="3">
+        <v>146.16485595703099</v>
+      </c>
+      <c r="C666" s="4">
+        <v>44.520010011339899</v>
+      </c>
+      <c r="D666">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668" spans="2:5">
+      <c r="B668" s="3">
+        <v>148.90319824218801</v>
+      </c>
+      <c r="C668" s="4">
+        <v>45.490945692627299</v>
+      </c>
+      <c r="D668">
+        <v>0</v>
+      </c>
+      <c r="E668" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="669" spans="2:5">
+      <c r="B669" s="3">
+        <v>148.82354736328099</v>
+      </c>
+      <c r="C669" s="4">
+        <v>45.448570648115798</v>
+      </c>
+      <c r="D669">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="670" spans="2:5">
+      <c r="B670" s="3">
+        <v>148.88671875</v>
+      </c>
+      <c r="C670" s="4">
+        <v>45.4061637451601</v>
+      </c>
+      <c r="D670">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="671" spans="2:5">
+      <c r="B671" s="3">
+        <v>148.853759765625</v>
+      </c>
+      <c r="C671" s="4">
+        <v>45.340563138898602</v>
+      </c>
+      <c r="D671">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="672" spans="2:5">
+      <c r="B672" s="3">
+        <v>148.62579345703099</v>
+      </c>
+      <c r="C672" s="4">
+        <v>45.327047685672603</v>
+      </c>
+      <c r="D672">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="673" spans="2:4">
+      <c r="B673" s="3">
+        <v>148.40606689453099</v>
+      </c>
+      <c r="C673" s="4">
+        <v>45.230414929592897</v>
+      </c>
+      <c r="D673">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="674" spans="2:4">
+      <c r="B674" s="3">
+        <v>148.31268310546901</v>
+      </c>
+      <c r="C674" s="4">
+        <v>45.213003555994</v>
+      </c>
+      <c r="D674">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675" spans="2:4">
+      <c r="B675" s="3">
+        <v>147.92541503906301</v>
+      </c>
+      <c r="C675" s="4">
+        <v>44.9745137056399</v>
+      </c>
+      <c r="D675">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676" spans="2:4">
+      <c r="B676" s="3">
+        <v>147.77984619140599</v>
+      </c>
+      <c r="C676" s="4">
+        <v>44.949249266611503</v>
+      </c>
+      <c r="D676">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="677" spans="2:4">
+      <c r="B677" s="3">
+        <v>147.68646240234401</v>
+      </c>
+      <c r="C677" s="4">
+        <v>45.003651156871904</v>
+      </c>
+      <c r="D677">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678" spans="2:4">
+      <c r="B678" s="3">
+        <v>147.60681152343801</v>
+      </c>
+      <c r="C678" s="4">
+        <v>44.935640729718401</v>
+      </c>
+      <c r="D678">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="679" spans="2:4">
+      <c r="B679" s="3">
+        <v>147.65350341796901</v>
+      </c>
+      <c r="C679" s="4">
+        <v>44.904523389609302</v>
+      </c>
+      <c r="D679">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="680" spans="2:4">
+      <c r="B680" s="3">
+        <v>147.50518798828099</v>
+      </c>
+      <c r="C680" s="4">
+        <v>44.7798855027728</v>
+      </c>
+      <c r="D680">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="681" spans="2:4">
+      <c r="B681" s="3">
+        <v>147.34039306640599</v>
+      </c>
+      <c r="C681" s="4">
+        <v>44.707706221835402</v>
+      </c>
+      <c r="D681">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="682" spans="2:4">
+      <c r="B682" s="3">
+        <v>147.20855712890599</v>
+      </c>
+      <c r="C682" s="4">
+        <v>44.563077307578901</v>
+      </c>
+      <c r="D682">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="683" spans="2:4">
+      <c r="B683" s="3">
+        <v>146.97784423828099</v>
+      </c>
+      <c r="C683" s="4">
+        <v>44.429857265397203</v>
+      </c>
+      <c r="D683">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="684" spans="2:4">
+      <c r="B684" s="3">
+        <v>146.87072753906301</v>
+      </c>
+      <c r="C684" s="4">
+        <v>44.4416242175881</v>
+      </c>
+      <c r="D684">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685" spans="2:4">
+      <c r="B685" s="3">
+        <v>146.93389892578099</v>
+      </c>
+      <c r="C685" s="4">
+        <v>44.545462718849798</v>
+      </c>
+      <c r="D685">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686" spans="2:4">
+      <c r="B686" s="3">
+        <v>147.02728271484401</v>
+      </c>
+      <c r="C686" s="4">
+        <v>44.592423107178703</v>
+      </c>
+      <c r="D686">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687" spans="2:4">
+      <c r="B687" s="3">
+        <v>147.02728271484401</v>
+      </c>
+      <c r="C687" s="4">
+        <v>44.654977979262902</v>
+      </c>
+      <c r="D687">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="688" spans="2:4">
+      <c r="B688" s="3">
+        <v>147.117919921875</v>
+      </c>
+      <c r="C688" s="4">
+        <v>44.6354368225686</v>
+      </c>
+      <c r="D688">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689" spans="2:4">
+      <c r="B689" s="3">
+        <v>147.20306396484401</v>
+      </c>
+      <c r="C689" s="4">
+        <v>44.748683899968299</v>
+      </c>
+      <c r="D689">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690" spans="2:4">
+      <c r="B690" s="3">
+        <v>147.09045410156301</v>
+      </c>
+      <c r="C690" s="4">
+        <v>44.789632547614097</v>
+      </c>
+      <c r="D690">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691" spans="2:4">
+      <c r="B691" s="3">
+        <v>147.11585998535199</v>
+      </c>
+      <c r="C691" s="4">
+        <v>44.827143305192799</v>
+      </c>
+      <c r="D691">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692" spans="2:4">
+      <c r="B692" s="3">
+        <v>147.19276428222699</v>
+      </c>
+      <c r="C692" s="4">
+        <v>44.797428998555702</v>
+      </c>
+      <c r="D692">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693" spans="2:4">
+      <c r="B693" s="3">
+        <v>147.24151611328099</v>
+      </c>
+      <c r="C693" s="4">
+        <v>44.8086345514958</v>
+      </c>
+      <c r="D693">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694" spans="2:4">
+      <c r="B694" s="3">
+        <v>147.26417541503901</v>
+      </c>
+      <c r="C694" s="4">
+        <v>44.868036310187499</v>
+      </c>
+      <c r="D694">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695" spans="2:4">
+      <c r="B695" s="3">
+        <v>147.38433837890599</v>
+      </c>
+      <c r="C695" s="4">
+        <v>44.9142493687471</v>
+      </c>
+      <c r="D695">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696" spans="2:4">
+      <c r="B696" s="3">
+        <v>147.48664855957</v>
+      </c>
+      <c r="C696" s="4">
+        <v>44.989084282761397</v>
+      </c>
+      <c r="D696">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697" spans="2:4">
+      <c r="B697" s="3">
+        <v>147.51274108886699</v>
+      </c>
+      <c r="C697" s="4">
+        <v>44.9910267465945</v>
+      </c>
+      <c r="D697">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698" spans="2:4">
+      <c r="B698" s="3">
+        <v>147.52853393554699</v>
+      </c>
+      <c r="C698" s="4">
+        <v>45.090974638356599</v>
+      </c>
+      <c r="D698">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699" spans="2:4">
+      <c r="B699" s="3">
+        <v>147.49557495117199</v>
+      </c>
+      <c r="C699" s="4">
+        <v>45.109877155278099</v>
+      </c>
+      <c r="D699">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700" spans="2:4">
+      <c r="B700" s="3">
+        <v>147.50999450683599</v>
+      </c>
+      <c r="C700" s="4">
+        <v>45.1161766035749</v>
+      </c>
+      <c r="D700">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701" spans="2:4">
+      <c r="B701" s="3">
+        <v>147.57247924804699</v>
+      </c>
+      <c r="C701" s="4">
+        <v>45.103092356408602</v>
+      </c>
+      <c r="D701">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702" spans="2:4">
+      <c r="B702" s="3">
+        <v>147.63015747070301</v>
+      </c>
+      <c r="C702" s="4">
+        <v>45.075460206883598</v>
+      </c>
+      <c r="D702">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703" spans="2:4">
+      <c r="B703" s="3">
+        <v>147.69813537597699</v>
+      </c>
+      <c r="C703" s="4">
+        <v>45.102123033596399</v>
+      </c>
+      <c r="D703">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704" spans="2:4">
+      <c r="B704" s="3">
+        <v>147.69332885742199</v>
+      </c>
+      <c r="C704" s="4">
+        <v>45.144757668358203</v>
+      </c>
+      <c r="D704">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705" spans="2:4">
+      <c r="B705" s="3">
+        <v>147.73727416992199</v>
+      </c>
+      <c r="C705" s="4">
+        <v>45.192199649314503</v>
+      </c>
+      <c r="D705">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706" spans="2:4">
+      <c r="B706" s="3">
+        <v>147.82653808593801</v>
+      </c>
+      <c r="C706" s="4">
+        <v>45.216389518465498</v>
+      </c>
+      <c r="D706">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707" spans="2:4">
+      <c r="B707" s="3">
+        <v>147.84645080566401</v>
+      </c>
+      <c r="C707" s="4">
+        <v>45.2067148051106</v>
+      </c>
+      <c r="D707">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708" spans="2:4">
+      <c r="B708" s="3">
+        <v>147.88352966308599</v>
+      </c>
+      <c r="C708" s="4">
+        <v>45.2555552778921</v>
+      </c>
+      <c r="D708">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709" spans="2:4">
+      <c r="B709" s="3">
+        <v>147.86293029785199</v>
+      </c>
+      <c r="C709" s="4">
+        <v>45.262321932396297</v>
+      </c>
+      <c r="D709">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710" spans="2:4">
+      <c r="B710" s="3">
+        <v>147.85263061523401</v>
+      </c>
+      <c r="C710" s="4">
+        <v>45.364689854189798</v>
+      </c>
+      <c r="D710">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711" spans="2:4">
+      <c r="B711" s="3">
+        <v>147.91854858398401</v>
+      </c>
+      <c r="C711" s="4">
+        <v>45.435562827127796</v>
+      </c>
+      <c r="D711">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712" spans="2:4">
+      <c r="B712" s="3">
+        <v>147.96318054199199</v>
+      </c>
+      <c r="C712" s="4">
+        <v>45.419178341904598</v>
+      </c>
+      <c r="D712">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713" spans="2:4">
+      <c r="B713" s="3">
+        <v>148.03390502929699</v>
+      </c>
+      <c r="C713" s="4">
+        <v>45.266671498748998</v>
+      </c>
+      <c r="D713">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714" spans="2:4">
+      <c r="B714" s="3">
+        <v>148.14308166503901</v>
+      </c>
+      <c r="C714" s="4">
+        <v>45.254588547134198</v>
+      </c>
+      <c r="D714">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715" spans="2:4">
+      <c r="B715" s="3">
+        <v>148.34701538085901</v>
+      </c>
+      <c r="C715" s="4">
+        <v>45.292761898494</v>
+      </c>
+      <c r="D715">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716" spans="2:4">
+      <c r="B716" s="3">
+        <v>148.47953796386699</v>
+      </c>
+      <c r="C716" s="4">
+        <v>45.390735154248901</v>
+      </c>
+      <c r="D716">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="717" spans="2:4">
+      <c r="B717" s="3">
+        <v>148.48159790039099</v>
+      </c>
+      <c r="C717" s="4">
+        <v>45.416286468478503</v>
+      </c>
+      <c r="D717">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718" spans="2:4">
+      <c r="B718" s="3">
+        <v>148.57772827148401</v>
+      </c>
+      <c r="C718" s="4">
+        <v>45.485650554296299</v>
+      </c>
+      <c r="D718">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="719" spans="2:4">
+      <c r="B719" s="3">
+        <v>148.63815307617199</v>
+      </c>
+      <c r="C719" s="4">
+        <v>45.504421980400799</v>
+      </c>
+      <c r="D719">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="720" spans="2:4">
+      <c r="B720" s="3">
+        <v>148.65051269531301</v>
+      </c>
+      <c r="C720" s="4">
+        <v>45.536655719680297</v>
+      </c>
+      <c r="D720">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721" spans="2:4">
+      <c r="B721" s="3">
+        <v>148.78578186035199</v>
+      </c>
+      <c r="C721" s="4">
+        <v>45.5525252513401</v>
+      </c>
+      <c r="D721">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="722" spans="2:4">
+      <c r="B722" s="3">
+        <v>148.87023925781301</v>
+      </c>
+      <c r="C722" s="4">
+        <v>45.532326888097302</v>
+      </c>
+      <c r="D722">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="723" spans="2:4">
+      <c r="B723" s="3">
+        <v>148.90319824218801</v>
+      </c>
+      <c r="C723" s="4">
+        <v>45.489501613357902</v>
+      </c>
+      <c r="D723">
         <v>0</v>
       </c>
     </row>
